--- a/Mantenimiento/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/Mantenimiento/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,7 +1302,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JUAN_BAUTISTA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1419,11 +1329,6 @@
       </c>
       <c r="K19" t="n">
         <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
+++ b/Mantenimiento/excels/LORETO-MAYNAS-SAN_JUAN_BAUTISTA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>317</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-3.7739</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-73.27485</v>
-      </c>
-      <c r="I2" t="n">
-        <v>445</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-3.7739</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-73.27485</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>318 GLORIA CHAVEZ CULQUI</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-3.77391</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-73.29031000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>460</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-3.77391</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-73.29031</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>396 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-3.766563</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-73.278856</v>
-      </c>
-      <c r="I4" t="n">
-        <v>310</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-3.766563</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-73.278856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>474 ANGELITOS DEL SABER</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-3.77282</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-73.28157</v>
-      </c>
-      <c r="I5" t="n">
-        <v>139</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-3.77282</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-73.28157</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>APLICACION UNAP</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-3.7815</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-73.28538</v>
-      </c>
-      <c r="I6" t="n">
-        <v>898</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-3.7815</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-73.28538</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>690 SANTA MONICA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-3.76748</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-73.27315</v>
-      </c>
-      <c r="I7" t="n">
-        <v>203</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-3.76748</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-73.27315</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>60024 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-3.77449</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-73.29006</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2931</v>
-      </c>
-      <c r="J8" t="n">
-        <v>109</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-3.77449</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-73.29006</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>60027</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-3.786487</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-73.33911500000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1308</v>
-      </c>
-      <c r="J9" t="n">
-        <v>52</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-3.786487</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-73.339115</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>60093 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-3.80519</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-73.340785</v>
-      </c>
-      <c r="I10" t="n">
-        <v>917</v>
-      </c>
-      <c r="J10" t="n">
-        <v>48</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-3.80519</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-73.340785</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>60113</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-3.780437</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-73.312084</v>
-      </c>
-      <c r="I11" t="n">
-        <v>667</v>
-      </c>
-      <c r="J11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-3.780437</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-73.312084</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>601332</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-3.77915</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-73.28175</v>
-      </c>
-      <c r="I12" t="n">
-        <v>514</v>
-      </c>
-      <c r="J12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-3.77915</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-73.28175</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>601387</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-3.77069</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-73.27883</v>
-      </c>
-      <c r="I13" t="n">
-        <v>324</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-3.77069</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-73.27883</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>601411 MELVIN JONES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-3.761201</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-73.272904</v>
-      </c>
-      <c r="I14" t="n">
-        <v>840</v>
-      </c>
-      <c r="J14" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-3.761201</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-73.272904</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>6010275 FRANCISCO SECADA VIGNETTA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-3.78161</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-73.29532</v>
-      </c>
-      <c r="I15" t="n">
-        <v>784</v>
-      </c>
-      <c r="J15" t="n">
-        <v>36</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-3.78161</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-73.29532</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>COLEGIO NACIONAL IQUITOS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-3.7654</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-73.26864</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2432</v>
-      </c>
-      <c r="J16" t="n">
-        <v>144</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-3.7654</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-73.26864</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>601491 MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-3.79099</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-73.30119999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2305</v>
-      </c>
-      <c r="J17" t="n">
-        <v>81</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.79099</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-73.3012</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>FE Y ALEGRIA 46 WILHEM ROSSMAN</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-3.77839</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-73.29181</v>
-      </c>
-      <c r="I18" t="n">
-        <v>896</v>
-      </c>
-      <c r="J18" t="n">
-        <v>37</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.77839</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-73.29181</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>UNAP MARIA REICHE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-3.766469</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-73.273014</v>
-      </c>
-      <c r="I19" t="n">
-        <v>139</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.766469</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-73.273014</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
